--- a/measurements/38/Filled_2D_sections/axial/week38_axial_Batch_Allmarks.xlsx
+++ b/measurements/38/Filled_2D_sections/axial/week38_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,107 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +601,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14.39738251041047</v>
+        <v>5487.981859410431</v>
       </c>
       <c r="D2" t="n">
-        <v>40.60171356433776</v>
+        <v>792.7001219704038</v>
       </c>
       <c r="E2" t="n">
-        <v>17.57028809989371</v>
+        <v>343.0389581407819</v>
       </c>
       <c r="F2" t="n">
         <v>2.31081660889689</v>
@@ -525,24 +620,63 @@
         <v>0.1097500384646501</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5162919207317074</v>
+        <v>2.209821428571428</v>
       </c>
       <c r="J2" t="n">
-        <v>2.349657012195122</v>
+        <v>45.87425595238095</v>
       </c>
       <c r="K2" t="n">
-        <v>1.104563643292683</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>11.58083545918367</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>45.87425595238095</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32.60974702380953</v>
+      </c>
+      <c r="O2" t="n">
+        <v>16.94196428571428</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>9.103422619047619</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.06845238095238</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>10.76729910714286</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.209821428571428</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.82328869047619</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.376647534013606</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>14.59711481261154</v>
+      <c r="AH2" s="2" t="n">
+        <v>5564.115646258503</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +687,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.54759071980964</v>
+        <v>5545.238095238095</v>
       </c>
       <c r="D3" t="n">
-        <v>40.64804269337073</v>
+        <v>793.6046430610475</v>
       </c>
       <c r="E3" t="n">
-        <v>17.63090472395827</v>
+        <v>344.2224255629948</v>
       </c>
       <c r="F3" t="n">
         <v>2.305499537873116</v>
@@ -572,24 +706,63 @@
         <v>0.1106424189503307</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.57421875</v>
+        <v>1.715029761904762</v>
       </c>
       <c r="J3" t="n">
-        <v>2.387766768292683</v>
+        <v>46.61830357142857</v>
       </c>
       <c r="K3" t="n">
-        <v>1.107612423780488</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>10.70917038690476</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>46.61830357142857</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32.07403273809523</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16.06212797619047</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5.124627976190476</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.19308035714286</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.770833333333332</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.715029761904762</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4.877232142857142</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.467261904761905</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>32.68511242415847</v>
+      <c r="AH3" s="2" t="n">
+        <v>638.1379092335701</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +773,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14.54907792980369</v>
+        <v>5545.804988662131</v>
       </c>
       <c r="D4" t="n">
-        <v>38.81847702584616</v>
+        <v>757.8845514569963</v>
       </c>
       <c r="E4" t="n">
-        <v>18.00195841963698</v>
+        <v>351.4668072405315</v>
       </c>
       <c r="F4" t="n">
         <v>2.156347444037089</v>
@@ -619,24 +792,63 @@
         <v>0.1213300422725565</v>
       </c>
       <c r="H4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.71875</v>
+      </c>
+      <c r="J4" t="n">
+        <v>46.78199404761904</v>
+      </c>
+      <c r="K4" t="n">
+        <v>11.94820897108844</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>46.78199404761904</v>
+      </c>
+      <c r="N4" t="n">
+        <v>31.8656994047619</v>
+      </c>
+      <c r="O4" t="n">
+        <v>16.1328125</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5.453869047619047</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13.7109375</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.397631448412698</v>
+      </c>
+      <c r="Z4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.6108041158536586</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.396150914634147</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.233536585365854</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="AA4" t="n">
+        <v>1.71875</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.853050595238095</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.221726190476191</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>17.0884607515684</v>
+      <c r="AH4" s="2" t="n">
+        <v>333.6318527687163</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +859,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14.540749553837</v>
+        <v>5542.630385487528</v>
       </c>
       <c r="D5" t="n">
-        <v>36.05616400590757</v>
+        <v>703.9536782105763</v>
       </c>
       <c r="E5" t="n">
-        <v>18.03053337480964</v>
+        <v>352.0246992224738</v>
       </c>
       <c r="F5" t="n">
         <v>1.999728086595677</v>
@@ -666,23 +878,62 @@
         <v>0.1405521901359696</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5982278963414634</v>
+        <v>2.5390625</v>
       </c>
       <c r="J5" t="n">
-        <v>2.324409298780488</v>
+        <v>45.38132440476191</v>
       </c>
       <c r="K5" t="n">
-        <v>1.148113567073171</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>11.06837266156463</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>16.14397321428571</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>45.38132440476191</v>
+      </c>
+      <c r="R5" t="n">
+        <v>25.09951636904762</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5.306919642857142</v>
+      </c>
+      <c r="X5" t="n">
+        <v>11.6796875</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.336123511904761</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.5390625</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.951636904761904</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.53577628968254</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AH5" s="2" t="n">
         <v>1.906550861494358</v>
       </c>
     </row>
@@ -694,42 +945,81 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14.58506841165973</v>
+        <v>5559.523809523809</v>
       </c>
       <c r="D6" t="n">
-        <v>34.18965396357746</v>
+        <v>667.5122916698456</v>
       </c>
       <c r="E6" t="n">
-        <v>17.88072518604558</v>
+        <v>349.0998726799374</v>
       </c>
       <c r="F6" t="n">
         <v>1.912095488736645</v>
       </c>
       <c r="G6" t="n">
-        <v>0.15679381383829</v>
+        <v>0.1567938138382899</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5607850609756098</v>
+        <v>2.113095238095238</v>
       </c>
       <c r="J6" t="n">
-        <v>2.106612042682927</v>
+        <v>41.12909226190476</v>
       </c>
       <c r="K6" t="n">
-        <v>1.114195884146342</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>10.02192283163265</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>16.82291666666666</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>41.12909226190476</v>
+      </c>
+      <c r="R6" t="n">
+        <v>24.45452008928572</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10.94866071428571</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.606398809523809</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.455729166666666</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.113095238095238</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.53422619047619</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.925435799319728</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AH6" s="2" t="n">
         <v>0.1820207130779252</v>
       </c>
     </row>
@@ -741,43 +1031,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14.65318262938727</v>
+        <v>5585.487528344671</v>
       </c>
       <c r="D7" t="n">
-        <v>32.14273007904611</v>
+        <v>627.5485396385193</v>
       </c>
       <c r="E7" t="n">
-        <v>18.18177753541528</v>
+        <v>354.9775614057268</v>
       </c>
       <c r="F7" t="n">
         <v>1.767854106477602</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1782281519465412</v>
+        <v>0.1782281519465411</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5232469512195123</v>
+        <v>2.007068452380952</v>
       </c>
       <c r="J7" t="n">
-        <v>1.641387195121951</v>
+        <v>32.04613095238095</v>
       </c>
       <c r="K7" t="n">
-        <v>1.044512195121951</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>8.779180617559526</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>16.54947916666666</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>32.04613095238095</v>
+      </c>
+      <c r="R7" t="n">
+        <v>22.93712797619047</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10.21577380952381</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7.351190476190475</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.305803571428571</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.007068452380952</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.228050595238095</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.760623346560847</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>4.35</v>
+      <c r="AH7" s="2" t="n">
+        <v>15.65</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1117,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.89708506841166</v>
+        <v>5678.458049886621</v>
       </c>
       <c r="D8" t="n">
-        <v>36.95788505891474</v>
+        <v>721.5587082930973</v>
       </c>
       <c r="E8" t="n">
-        <v>17.62008397753646</v>
+        <v>344.0111633709499</v>
       </c>
       <c r="F8" t="n">
         <v>2.097486317660672</v>
@@ -807,24 +1136,60 @@
         <v>0.1370556491275268</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5561166158536586</v>
+        <v>1.58110119047619</v>
       </c>
       <c r="J8" t="n">
-        <v>1.609756097560976</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="K8" t="n">
-        <v>1.010353150406504</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>8.810557208994707</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14.82328869047619</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>31.42857142857143</v>
+      </c>
+      <c r="R8" t="n">
+        <v>21.49962797619047</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10.85751488095238</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.58110119047619</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.748883928571428</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.791869588744588</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6844083460365853</v>
+      <c r="AH8" s="2" t="n">
+        <v>1.891834077380952</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1200,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.70672218917311</v>
+        <v>5605.895691609977</v>
       </c>
       <c r="D9" t="n">
-        <v>38.28392240477771</v>
+        <v>747.4480088551838</v>
       </c>
       <c r="E9" t="n">
-        <v>17.54517985844031</v>
+        <v>342.5487496171679</v>
       </c>
       <c r="F9" t="n">
         <v>2.182019375900601</v>
@@ -854,24 +1219,63 @@
         <v>0.126093557591968</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5034298780487805</v>
+        <v>1.703869047619047</v>
       </c>
       <c r="J9" t="n">
-        <v>1.55030487804878</v>
+        <v>30.26785714285714</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9393646559233451</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>9.695172991071427</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>15.78683035714286</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>30.26785714285714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>23.18033854166666</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14.6484375</v>
+      </c>
+      <c r="U9" t="n">
+        <v>11.18117559523809</v>
+      </c>
+      <c r="V9" t="n">
+        <v>9.828869047619047</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.388020833333333</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.971436838624339</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.786023246951219</v>
+      <c r="AH9" s="2" t="n">
+        <v>34.86997767857143</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1286,82 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14.86079714455681</v>
+        <v>5664.625850340136</v>
       </c>
       <c r="D10" t="n">
-        <v>34.42763834464841</v>
+        <v>672.1586533955165</v>
       </c>
       <c r="E10" t="n">
-        <v>17.42149528352226</v>
+        <v>340.1339555354345</v>
       </c>
       <c r="F10" t="n">
         <v>1.976158635315939</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1575569284376349</v>
+        <v>0.157556928437635</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5782202743902439</v>
+        <v>2.159598214285714</v>
       </c>
       <c r="J10" t="n">
-        <v>1.580792682926829</v>
+        <v>30.86309523809524</v>
       </c>
       <c r="K10" t="n">
-        <v>0.902121443089431</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>10.30838116496599</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>30.86309523809524</v>
+      </c>
+      <c r="N10" t="n">
+        <v>22.53162202380952</v>
+      </c>
+      <c r="O10" t="n">
+        <v>15.31994047619047</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5.048363095238095</v>
+      </c>
+      <c r="X10" t="n">
+        <v>14.24107142857143</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.159598214285714</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.404761904761904</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.588169642857142</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.136037560794135</v>
+      <c r="AH10" s="2" t="n">
+        <v>9.194163457483688</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1372,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14.95687091017252</v>
+        <v>5701.247165532879</v>
       </c>
       <c r="D11" t="n">
-        <v>33.4795881916837</v>
+        <v>653.649102790015</v>
       </c>
       <c r="E11" t="n">
-        <v>17.08003186888811</v>
+        <v>333.4672888687679</v>
       </c>
       <c r="F11" t="n">
         <v>1.960159585689531</v>
@@ -948,16 +1391,63 @@
         <v>0.1676835248207811</v>
       </c>
       <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.618303571428571</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.50297619047619</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.765279549319727</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.8288871951219513</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.613567073170732</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.204331808943089</v>
+      <c r="M11" t="n">
+        <v>31.50297619047619</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22.85342261904762</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16.18303571428571</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5.392485119047619</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.410714285714286</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.093129960317461</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.618303571428571</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.915550595238095</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.12313988095238</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>3.05</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1458,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.92415229030339</v>
+        <v>5688.775510204081</v>
       </c>
       <c r="D12" t="n">
-        <v>33.43571036327176</v>
+        <v>652.7924404257819</v>
       </c>
       <c r="E12" t="n">
-        <v>17.03962075419542</v>
+        <v>332.678309962863</v>
       </c>
       <c r="F12" t="n">
         <v>1.962233247183002</v>
@@ -987,16 +1477,63 @@
         <v>0.167756140943362</v>
       </c>
       <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.134300595238095</v>
+      </c>
+      <c r="J12" t="n">
+        <v>31.97172619047619</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.591541108630953</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.8979611280487805</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.637576219512195</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.242759146341464</v>
+      <c r="M12" t="n">
+        <v>31.97172619047619</v>
+      </c>
+      <c r="N12" t="n">
+        <v>23.28683035714285</v>
+      </c>
+      <c r="O12" t="n">
+        <v>17.53162202380952</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.081845238095238</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9.754464285714285</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.319754464285715</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.134300595238095</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.780505952380953</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.822278911564626</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>34.47643849206349</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1544,82 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.55621653777513</v>
+        <v>5548.526077097506</v>
       </c>
       <c r="D13" t="n">
-        <v>32.0047580178191</v>
+        <v>624.8547993955158</v>
       </c>
       <c r="E13" t="n">
-        <v>17.06819573262843</v>
+        <v>333.2362023989359</v>
       </c>
       <c r="F13" t="n">
-        <v>1.875110791976517</v>
+        <v>1.875110791976518</v>
       </c>
       <c r="G13" t="n">
         <v>0.1785785431648078</v>
       </c>
       <c r="H13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.912202380952381</v>
+      </c>
+      <c r="J13" t="n">
+        <v>30.72730654761905</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9.256324404761903</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>1.237042682926829</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.573837652439025</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.352642276422764</v>
+      <c r="M13" t="n">
+        <v>30.72730654761905</v>
+      </c>
+      <c r="N13" t="n">
+        <v>24.34709821428571</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24.15178571428571</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.996279761904762</v>
+      </c>
+      <c r="X13" t="n">
+        <v>8.188244047619047</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.192867772108843</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.912202380952381</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.760044642857142</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.253720238095237</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>25.70709325396825</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1630,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14.56484235574063</v>
+        <v>5551.814058956916</v>
       </c>
       <c r="D14" t="n">
-        <v>30.19049519736592</v>
+        <v>589.4334776628584</v>
       </c>
       <c r="E14" t="n">
-        <v>16.9253209800255</v>
+        <v>330.446742943355</v>
       </c>
       <c r="F14" t="n">
         <v>1.783747276225685</v>
@@ -1065,16 +1649,63 @@
         <v>0.2008053036858279</v>
       </c>
       <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.754092261904762</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.93563988095238</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9.066618835034012</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>1.178353658536585</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.328410823170732</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.263306656504065</v>
+      <c r="M14" t="n">
+        <v>25.93563988095238</v>
+      </c>
+      <c r="N14" t="n">
+        <v>25.05208333333333</v>
+      </c>
+      <c r="O14" t="n">
+        <v>23.00595238095238</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>5.269717261904762</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7.191220238095238</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.202256944444444</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.754092261904762</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4.581473214285714</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.145089285714286</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>18.17485119047619</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1716,82 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14.55472932778108</v>
+        <v>5547.959183673469</v>
       </c>
       <c r="D15" t="n">
-        <v>29.52920989001669</v>
+        <v>576.5226692812784</v>
       </c>
       <c r="E15" t="n">
-        <v>16.93960846342692</v>
+        <v>330.7256890478588</v>
       </c>
       <c r="F15" t="n">
-        <v>1.743204983383829</v>
+        <v>1.74320498338383</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2097540445813591</v>
+        <v>0.209754044581359</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6335746951219512</v>
+        <v>2.085193452380952</v>
       </c>
       <c r="J15" t="n">
-        <v>1.671589176829268</v>
+        <v>32.63578869047619</v>
       </c>
       <c r="K15" t="n">
-        <v>1.191072789634146</v>
+        <v>9.698926445578229</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>32.63578869047619</v>
+      </c>
+      <c r="N15" t="n">
+        <v>25.40178571428571</v>
+      </c>
+      <c r="O15" t="n">
+        <v>22.60974702380952</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>5.050223214285714</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12.36979166666667</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7.270461309523808</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.085193452380952</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.561011904761904</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.130890376984127</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>16.02529761904762</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1802,79 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14.99970255800119</v>
+        <v>5717.573696145124</v>
       </c>
       <c r="D16" t="n">
-        <v>27.06651327086658</v>
+        <v>528.4414495740617</v>
       </c>
       <c r="E16" t="n">
-        <v>16.43159805274591</v>
+        <v>320.8073905536107</v>
       </c>
       <c r="F16" t="n">
-        <v>1.64722342793332</v>
+        <v>1.647223427933319</v>
       </c>
       <c r="G16" t="n">
         <v>0.2572929489961728</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5323932926829269</v>
+        <v>1.925223214285714</v>
       </c>
       <c r="J16" t="n">
-        <v>1.292397103658537</v>
+        <v>25.23251488095238</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8387004573170731</v>
+        <v>6.455129794973543</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>25.23251488095238</v>
+      </c>
+      <c r="N16" t="n">
+        <v>19.25223214285714</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5.855654761904762</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.61941964285714</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8.395089285714285</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.925223214285714</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.272693452380953</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.702922077922078</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>36.05059523809524</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1885,79 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14.78346222486615</v>
+        <v>5635.147392290249</v>
       </c>
       <c r="D17" t="n">
-        <v>27.42226414273425</v>
+        <v>535.3870618343353</v>
       </c>
       <c r="E17" t="n">
-        <v>16.36607872276771</v>
+        <v>319.5282036349887</v>
       </c>
       <c r="F17" t="n">
         <v>1.675554945521904</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2470468952471511</v>
+        <v>0.247046895247151</v>
       </c>
       <c r="H17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.6796875</v>
+      </c>
+      <c r="J17" t="n">
+        <v>35.02046130952381</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7.608871673669468</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>1.268673780487805</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.793730945121951</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.531202362804878</v>
+      <c r="M17" t="n">
+        <v>35.02046130952381</v>
+      </c>
+      <c r="N17" t="n">
+        <v>24.76934523809524</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.806547619047619</v>
+      </c>
+      <c r="X17" t="n">
+        <v>9.341517857142856</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.578776041666667</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.6796875</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.341517857142857</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.418686224489796</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>23.43422619047619</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1968,79 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.57376561570494</v>
+        <v>5555.215419501134</v>
       </c>
       <c r="D18" t="n">
-        <v>27.08181611503043</v>
+        <v>528.7402193886893</v>
       </c>
       <c r="E18" t="n">
-        <v>16.29709271686833</v>
+        <v>318.1813339960007</v>
       </c>
       <c r="F18" t="n">
         <v>1.661757503962615</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2497043308885304</v>
+        <v>0.2497043308885303</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5042873475609756</v>
+        <v>1.519717261904762</v>
       </c>
       <c r="J18" t="n">
-        <v>1.825647865853659</v>
+        <v>35.64360119047619</v>
       </c>
       <c r="K18" t="n">
-        <v>1.199790396341464</v>
+        <v>7.374648644179895</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>35.64360119047619</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24.78422619047619</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.756324404761904</v>
+      </c>
+      <c r="X18" t="n">
+        <v>9.845610119047619</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.112764550264549</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.519717261904762</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.135044642857142</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.47156675170068</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>5.7</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +2051,79 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14.36020226055919</v>
+        <v>5473.809523809524</v>
       </c>
       <c r="D19" t="n">
-        <v>26.75709151349417</v>
+        <v>522.4003581206003</v>
       </c>
       <c r="E19" t="n">
-        <v>16.06155969166174</v>
+        <v>313.5828320753006</v>
       </c>
       <c r="F19" t="n">
         <v>1.665908668096844</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2520534306526479</v>
+        <v>0.252053430652648</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.582983993902439</v>
+        <v>1.655505952380952</v>
       </c>
       <c r="J19" t="n">
-        <v>1.81030868902439</v>
+        <v>35.34412202380952</v>
       </c>
       <c r="K19" t="n">
-        <v>1.249364837398374</v>
+        <v>7.814907212885156</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>35.34412202380952</v>
+      </c>
+      <c r="N19" t="n">
+        <v>26.45089285714285</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.613095238095238</v>
+      </c>
+      <c r="X19" t="n">
+        <v>11.38206845238095</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.91869212962963</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.655505952380952</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.714657738095238</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.965029761904762</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>11.66759672619047</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2134,82 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14.02082093991672</v>
+        <v>5344.444444444444</v>
       </c>
       <c r="D20" t="n">
-        <v>28.04660510726091</v>
+        <v>547.5765759036655</v>
       </c>
       <c r="E20" t="n">
-        <v>15.79398504699149</v>
+        <v>308.3587556793576</v>
       </c>
       <c r="F20" t="n">
         <v>1.775777615580519</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2239869455942306</v>
+        <v>0.2239869455942305</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5013338414634146</v>
+        <v>1.402529761904762</v>
       </c>
       <c r="J20" t="n">
-        <v>1.708174542682927</v>
+        <v>33.35007440476191</v>
       </c>
       <c r="K20" t="n">
-        <v>1.098275533536585</v>
+        <v>8.527004551820729</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>33.35007440476191</v>
+      </c>
+      <c r="N20" t="n">
+        <v>28.82254464285714</v>
+      </c>
+      <c r="O20" t="n">
+        <v>13.80952380952381</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.575892857142857</v>
+      </c>
+      <c r="X20" t="n">
+        <v>9.787946428571429</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.384626116071428</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.402529761904762</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.49032738095238</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.983320932539682</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>8.415643601190474</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2220,79 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13.9098750743605</v>
+        <v>5302.154195011338</v>
       </c>
       <c r="D21" t="n">
-        <v>26.56196953319922</v>
+        <v>518.5908337434132</v>
       </c>
       <c r="E21" t="n">
-        <v>15.88317654190994</v>
+        <v>310.1001134372893</v>
       </c>
       <c r="F21" t="n">
         <v>1.672333582839164</v>
       </c>
       <c r="G21" t="n">
-        <v>0.247749362218165</v>
+        <v>0.2477493622181651</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5013338414634146</v>
+        <v>1.402529761904762</v>
       </c>
       <c r="J21" t="n">
-        <v>1.518387957317073</v>
+        <v>29.64471726190476</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9449314024390245</v>
+        <v>7.802214635854344</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29.64471726190476</v>
+      </c>
+      <c r="N21" t="n">
+        <v>21.50483630952381</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5.398065476190476</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.529529389880953</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.402529761904762</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.361979166666666</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.035980017006803</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>7.196800595238095</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2302,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>5.364583333333333</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2324,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>10.79008556547619</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2341,90 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>7.50123971029384</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>1.891834077380952</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>4.436197916666666</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>3.084578579695767</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/38/Filled_2D_sections/axial/week38_axial_Batch_Allmarks.xlsx
+++ b/measurements/38/Filled_2D_sections/axial/week38_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2430,4 +2636,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week38_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5564.115646258502</v>
+      </c>
+      <c r="D10" t="n">
+        <v>107.8640893964689</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5302.154195011338</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5717.573696145124</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>638.1379092335701</v>
+      </c>
+      <c r="D11" t="n">
+        <v>93.19413264398551</v>
+      </c>
+      <c r="E11" t="n">
+        <v>518.5908337434132</v>
+      </c>
+      <c r="F11" t="n">
+        <v>793.6046430610475</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.906550861494358</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2163392015001363</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.647223427933319</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.31081660889689</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1820207130779252</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05084762332996928</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1097500384646501</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2572929489961728</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>18</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0177.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0179.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0181.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0183.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>18</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0185.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>17</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>17</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0187.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>18</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>18</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0189.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>17</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>17</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0191.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>17</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>17</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0192.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>17</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>17</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.565247584249853</v>
+      </c>
+      <c r="E40" t="n">
+        <v>14</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.8255779474818964</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.105131574835269</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.916685735984467</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>61</v>
+      </c>
+      <c r="C48" t="n">
+        <v>25.81451868657299</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8.355423489665561</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.80952380952381</v>
+      </c>
+      <c r="F48" t="n">
+        <v>46.78199404761904</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>114</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7.459844272138681</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.369139974818786</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.575892857142857</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14.6484375</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>138</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.04264255521049</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.8036098158483591</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.402529761904762</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.951636904761904</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>